--- a/tests/fixtures/template_fixture.xlsx
+++ b/tests/fixtures/template_fixture.xlsx
@@ -17,7 +17,6 @@
     <sheet name="Interfaces" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Vendor info" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Accounts" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Notes" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -744,44 +743,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACME</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>a migration note</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/tests/fixtures/template_fixture.xlsx
+++ b/tests/fixtures/template_fixture.xlsx
@@ -422,11 +422,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A5:R7"/>
+  <dimension ref="A5:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="5">
@@ -517,7 +517,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>URL CATEGORY</t>
+          <t>URL NOTE</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>URL CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -603,6 +608,11 @@
         </is>
       </c>
       <c r="R6" t="inlineStr">
+        <is>
+          <t>vendor note</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
@@ -850,7 +860,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -923,7 +933,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -976,7 +986,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -1008,8 +1018,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1029,7 +1042,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -1047,6 +1065,11 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Support</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>second url note</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1130,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>

--- a/tests/fixtures/template_fixture.xlsx
+++ b/tests/fixtures/template_fixture.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Interfaces" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Vendor info" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Accounts" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="External note" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,6 +754,87 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10.57" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ORG CODE</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>NOTE TYPE</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>NOTE TITLE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CONTENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ACME</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>first note</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>first note body</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACME</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Follow-up</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>second note</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/tests/fixtures/template_fixture.xlsx
+++ b/tests/fixtures/template_fixture.xlsx
@@ -433,12 +433,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORG CODE</t>
+          <t>ORG CODE*</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ORG NAME</t>
+          <t>ORG NAME*</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -453,7 +453,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ORG status (Active/Inactive/Pending)</t>
+          <t>ORG status (Active/Inactive/Pending)*</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -652,98 +652,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A2:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ACCOUNT NAME</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ACCOUNT NUMBER</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ACCOUNTING CODE</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>PAYMENT METHOD</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ACCOUNT STATUS</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>LIBRARY EDI CODE</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ACCOUNT NAME*</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ACCOUNT NUMBER*</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ACCOUNTING CODE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PAYMENT METHOD</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ACCOUNT STATUS*</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>LIBRARY EDI CODE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>ACME</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Main Account</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>SYS1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>EFT</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>acct note</t>
         </is>
@@ -760,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A2:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.57" customWidth="1" min="1" max="1"/>
@@ -769,47 +769,26 @@
     <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>NOTE TYPE</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>NOTE TITLE</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>CONTENTS</t>
-        </is>
-      </c>
-    </row>
+    <row r="1" ht="15.75" customHeight="1"/>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ACME</t>
+          <t>ORG CODE*</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>NOTE TYPE*</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>first note</t>
+          <t>NOTE TITLE*</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>first note body</t>
+          <t>CONTENTS</t>
         </is>
       </c>
     </row>
@@ -821,10 +800,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>first note</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>first note body</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACME</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Follow-up</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>second note</t>
         </is>
@@ -841,40 +842,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A2:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ALT NAME</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ACME</t>
+          <t>ORG CODE*</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Acme Corp</t>
+          <t>ALT NAME*</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Formal name</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
@@ -885,6 +869,23 @@
         </is>
       </c>
       <c r="B3" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Formal name</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACME</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Acme Inc</t>
         </is>
@@ -901,83 +902,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A2:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADDR1 </t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ADDR2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>CITY</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>REGION</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>POSTAL CODE</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>COUNTRY</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>CATEGORIES</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADDR1 </t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ADDR2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CITY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>POSTAL CODE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>COUNTRY</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CATEGORIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>ACME</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>2 Warehouse Rd</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Springfield</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>62702</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
@@ -994,43 +995,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A2:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>TYPE</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>CATEGORIES</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PHONE*</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CATEGORIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>ACME</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>555-3000</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
@@ -1047,43 +1048,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A2:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>EMAIL</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>CATEGORIES</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMAIL*</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CATEGORIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>ACME</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>sales@acme.example</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
@@ -1100,56 +1101,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A2:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>CATEGORIES</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>URL*</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CATEGORIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>ACME</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>https://support.acme.example</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>second url note</t>
         </is>
@@ -1166,93 +1167,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A2:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>LAST NAME</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>FIRST NAME</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>TITLE</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>EMAIL</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PHONE </t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>CATEGORIES</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LAST NAME*</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FIRST NAME*</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TITLE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PHONE </t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CATEGORIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>ACME</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Smith</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Jo</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>a note</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>jo@acme.example</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>555-4000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>main contact</t>
         </is>
@@ -1269,88 +1270,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A2:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>NAME</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>TYPE</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>USERNAME</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>PASSWORD</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NAME</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>USERNAME*</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PASSWORD*</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>ACME</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Acme Admin</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://admin.acme.example</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>iface note</t>
         </is>
@@ -1367,117 +1368,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A2:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>PAYMENT METHOD</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>CURRENCIES</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>CLAIMING INTERVAL</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>DISCOUNT %</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>EXP ACTIVATION INTERVAL</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>EXP INVOICE INTERVAL</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>EXP RECEIPT INTERVAL</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>RENEWAL ACTIVATION INTERVAL</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>SUBSCRIPTION INTERVAL</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>EXPORT TO ACCOUNTING (Y/)</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>TAX ID</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>TAX %</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>LIABLE FOR VAT (Y/N)</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PAYMENT METHOD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CURRENCIES</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CLAIMING INTERVAL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DISCOUNT %</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EXP ACTIVATION INTERVAL</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>EXP INVOICE INTERVAL</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EXP RECEIPT INTERVAL</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>RENEWAL ACTIVATION INTERVAL</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SUBSCRIPTION INTERVAL</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>EXPORT TO ACCOUNTING (Y/)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>TAX ID</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>TAX %</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>LIABLE FOR VAT (Y/N)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>ACME</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>EFT</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>30</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>5</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>12-345</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/tests/fixtures/template_fixture.xlsx
+++ b/tests/fixtures/template_fixture.xlsx
@@ -423,13 +423,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A5:S7"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -448,80 +452,130 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>ALT NAME DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Vendor (Yes/No)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>ORG status (Active/Inactive/Pending)*</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDR1 </t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>ADDR2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>CITY</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>REGION</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>POSTAL CODE</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>COUNTRY</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ADDR LANGUAGE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ADDR CATEGORIES</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>PHONE</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>PHONE TYPE</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>PHONE LANGUAGE</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>PHONE CATEGORIES</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>FAX</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>EMAIL DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>EMAIL LANGUAGE</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>EMAIL CATEGORIES</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>URL DESCRIPTION</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>URL LANGUAGE</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>URL NOTE</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>URL CATEGORIES</t>
         </is>
@@ -545,75 +599,125 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Primary alias note</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>A test vendor</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>1 Main St</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Springfield</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>62701</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>555-1000</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>555-2000</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>info@acme.example</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Primary contact email</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>https://acme.example</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Main website</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>vendor note</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
@@ -630,12 +734,12 @@
           <t>Solo Co</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1048,9 +1152,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
@@ -1069,6 +1174,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>LANGUAGE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>CATEGORIES</t>
         </is>
       </c>
@@ -1087,6 +1197,11 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>Sales</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>fra</t>
         </is>
       </c>
     </row>
